--- a/Results_2b/Results_Alpha05/Results_SegRec/Results_Cross/Results_MSVT_SE_SE_Net/seed_results_MSVT_SE_SE_Net_balanced.xlsx
+++ b/Results_2b/Results_Alpha05/Results_SegRec/Results_Cross/Results_MSVT_SE_SE_Net/seed_results_MSVT_SE_SE_Net_balanced.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,34 +490,34 @@
         <v>42</v>
       </c>
       <c r="B2" t="n">
-        <v>0.71</v>
+        <v>70.94</v>
       </c>
       <c r="C2" t="n">
-        <v>0.75</v>
+        <v>75.36</v>
       </c>
       <c r="D2" t="n">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="E2" t="n">
-        <v>0.93</v>
+        <v>93.12</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99</v>
+        <v>99.06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.87</v>
+        <v>86.88</v>
       </c>
       <c r="H2" t="n">
-        <v>0.93</v>
+        <v>92.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.95</v>
+        <v>94.69</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9</v>
+        <v>90.31</v>
       </c>
       <c r="K2" t="n">
-        <v>0.87</v>
+        <v>87.47110000000001</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>71</v>
       </c>
       <c r="B3" t="n">
-        <v>0.73</v>
+        <v>73.11999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6</v>
+        <v>60.36</v>
       </c>
       <c r="D3" t="n">
-        <v>0.87</v>
+        <v>86.87</v>
       </c>
       <c r="E3" t="n">
-        <v>0.91</v>
+        <v>90.62</v>
       </c>
       <c r="F3" t="n">
-        <v>0.99</v>
+        <v>99.06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.87</v>
+        <v>86.56</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91</v>
+        <v>91.25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>89.69</v>
       </c>
       <c r="K3" t="n">
-        <v>0.86</v>
+        <v>85.73220000000001</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>101</v>
       </c>
       <c r="B4" t="n">
-        <v>0.73</v>
+        <v>73.44000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.68</v>
+        <v>67.86</v>
       </c>
       <c r="D4" t="n">
-        <v>0.82</v>
+        <v>81.88</v>
       </c>
       <c r="E4" t="n">
-        <v>0.96</v>
+        <v>96.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.98</v>
+        <v>97.81</v>
       </c>
       <c r="G4" t="n">
-        <v>0.88</v>
+        <v>88.44</v>
       </c>
       <c r="H4" t="n">
-        <v>0.92</v>
+        <v>91.86999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.95</v>
+        <v>95</v>
       </c>
       <c r="J4" t="n">
-        <v>0.89</v>
+        <v>89.05999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.87</v>
+        <v>86.8456</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>113</v>
       </c>
       <c r="B5" t="n">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>0.72</v>
+        <v>72.14</v>
       </c>
       <c r="D5" t="n">
-        <v>0.82</v>
+        <v>82.19</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.98</v>
+        <v>98.11999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.88</v>
+        <v>87.81</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92</v>
+        <v>92.19000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.93</v>
+        <v>93.44</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>0.87</v>
+        <v>87.2167</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>127</v>
       </c>
       <c r="B6" t="n">
-        <v>0.79</v>
+        <v>79.06</v>
       </c>
       <c r="C6" t="n">
-        <v>0.71</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.84</v>
+        <v>84.06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.96</v>
+        <v>95.63000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.99</v>
+        <v>99.06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.87</v>
+        <v>86.56</v>
       </c>
       <c r="H6" t="n">
-        <v>0.95</v>
+        <v>94.69</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.37</v>
       </c>
       <c r="J6" t="n">
-        <v>0.86</v>
+        <v>86.25</v>
       </c>
       <c r="K6" t="n">
-        <v>0.88</v>
+        <v>87.86109999999999</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>131</v>
       </c>
       <c r="B7" t="n">
-        <v>0.71</v>
+        <v>71.25</v>
       </c>
       <c r="C7" t="n">
-        <v>0.72</v>
+        <v>71.78999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.84</v>
+        <v>83.75</v>
       </c>
       <c r="E7" t="n">
-        <v>0.91</v>
+        <v>90.62</v>
       </c>
       <c r="F7" t="n">
-        <v>0.97</v>
+        <v>96.56</v>
       </c>
       <c r="G7" t="n">
-        <v>0.91</v>
+        <v>90.62</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92</v>
+        <v>91.56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.95</v>
+        <v>95</v>
       </c>
       <c r="J7" t="n">
-        <v>0.91</v>
+        <v>90.94</v>
       </c>
       <c r="K7" t="n">
-        <v>0.87</v>
+        <v>86.8989</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>139</v>
       </c>
       <c r="B8" t="n">
-        <v>0.78</v>
+        <v>77.5</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.86</v>
+        <v>86.25</v>
       </c>
       <c r="E8" t="n">
-        <v>0.92</v>
+        <v>91.56</v>
       </c>
       <c r="F8" t="n">
-        <v>0.98</v>
+        <v>98.11999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.89</v>
+        <v>89.05999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.92</v>
+        <v>91.86999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.96</v>
+        <v>96.25</v>
       </c>
       <c r="J8" t="n">
-        <v>0.88</v>
+        <v>88.44</v>
       </c>
       <c r="K8" t="n">
-        <v>0.88</v>
+        <v>87.5133</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>149</v>
       </c>
       <c r="B9" t="n">
-        <v>0.74</v>
+        <v>73.75</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6899999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.85</v>
+        <v>85</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9399999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="F9" t="n">
-        <v>0.97</v>
+        <v>97.19</v>
       </c>
       <c r="G9" t="n">
-        <v>0.86</v>
+        <v>86.25</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91</v>
+        <v>91.25</v>
       </c>
       <c r="I9" t="n">
-        <v>0.95</v>
+        <v>94.69</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>90.31</v>
       </c>
       <c r="K9" t="n">
-        <v>0.87</v>
+        <v>86.7911</v>
       </c>
     </row>
     <row r="10">
@@ -770,34 +770,34 @@
         <v>157</v>
       </c>
       <c r="B10" t="n">
-        <v>0.73</v>
+        <v>73.11999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.68</v>
+        <v>67.86</v>
       </c>
       <c r="D10" t="n">
-        <v>0.84</v>
+        <v>84.06</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.98</v>
+        <v>98.11999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.88</v>
+        <v>88.12</v>
       </c>
       <c r="H10" t="n">
-        <v>0.92</v>
+        <v>92.19000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>95.94</v>
       </c>
       <c r="J10" t="n">
-        <v>0.88</v>
+        <v>88.12</v>
       </c>
       <c r="K10" t="n">
-        <v>0.87</v>
+        <v>86.8433</v>
       </c>
     </row>
     <row r="11">
@@ -805,34 +805,34 @@
         <v>163</v>
       </c>
       <c r="B11" t="n">
-        <v>0.75</v>
+        <v>74.69</v>
       </c>
       <c r="C11" t="n">
-        <v>0.66</v>
+        <v>65.71000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.87</v>
+        <v>86.56</v>
       </c>
       <c r="E11" t="n">
-        <v>0.96</v>
+        <v>95.94</v>
       </c>
       <c r="F11" t="n">
-        <v>0.99</v>
+        <v>99.06</v>
       </c>
       <c r="G11" t="n">
-        <v>0.85</v>
+        <v>85.31</v>
       </c>
       <c r="H11" t="n">
-        <v>0.93</v>
+        <v>93.13</v>
       </c>
       <c r="I11" t="n">
-        <v>0.95</v>
+        <v>95</v>
       </c>
       <c r="J11" t="n">
-        <v>0.88</v>
+        <v>87.81</v>
       </c>
       <c r="K11" t="n">
-        <v>0.87</v>
+        <v>87.02330000000001</v>
       </c>
     </row>
     <row r="12">
@@ -840,34 +840,34 @@
         <v>173</v>
       </c>
       <c r="B12" t="n">
-        <v>0.76</v>
+        <v>75.62</v>
       </c>
       <c r="C12" t="n">
-        <v>0.72</v>
+        <v>71.78999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.82</v>
+        <v>82.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.95</v>
+        <v>94.69</v>
       </c>
       <c r="F12" t="n">
-        <v>0.99</v>
+        <v>98.75</v>
       </c>
       <c r="G12" t="n">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>90.31</v>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>95.30999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="K12" t="n">
-        <v>0.87</v>
+        <v>87.3856</v>
       </c>
     </row>
     <row r="13">
@@ -875,34 +875,34 @@
         <v>181</v>
       </c>
       <c r="B13" t="n">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="C13" t="n">
-        <v>0.71</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="E13" t="n">
-        <v>0.92</v>
+        <v>92.19000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99</v>
+        <v>98.75</v>
       </c>
       <c r="G13" t="n">
-        <v>0.92</v>
+        <v>91.86999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>0.95</v>
+        <v>95.30999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.91</v>
+        <v>90.94</v>
       </c>
       <c r="K13" t="n">
-        <v>0.88</v>
+        <v>87.72329999999999</v>
       </c>
     </row>
     <row r="14">
@@ -910,34 +910,34 @@
         <v>322</v>
       </c>
       <c r="B14" t="n">
-        <v>0.79</v>
+        <v>79.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6899999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.86</v>
+        <v>85.61999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9399999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="F14" t="n">
-        <v>0.98</v>
+        <v>98.44000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.88</v>
+        <v>88.12</v>
       </c>
       <c r="H14" t="n">
-        <v>0.93</v>
+        <v>93.44</v>
       </c>
       <c r="I14" t="n">
-        <v>0.95</v>
+        <v>95.30999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.88</v>
+        <v>88.12</v>
       </c>
       <c r="K14" t="n">
-        <v>0.88</v>
+        <v>87.8656</v>
       </c>
     </row>
     <row r="15">
@@ -945,34 +945,34 @@
         <v>521</v>
       </c>
       <c r="B15" t="n">
-        <v>0.73</v>
+        <v>73.44000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6899999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.86</v>
+        <v>85.61999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.37</v>
       </c>
       <c r="F15" t="n">
-        <v>0.99</v>
+        <v>99.06</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9</v>
+        <v>90.31</v>
       </c>
       <c r="H15" t="n">
-        <v>0.92</v>
+        <v>92.19000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9399999999999999</v>
+        <v>94.37</v>
       </c>
       <c r="J15" t="n">
-        <v>0.88</v>
+        <v>87.81</v>
       </c>
       <c r="K15" t="n">
-        <v>0.87</v>
+        <v>87.34439999999999</v>
       </c>
     </row>
     <row r="16">
@@ -982,34 +982,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.75</v>
+        <v>74.6421</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6899999999999999</v>
+        <v>69.3121</v>
       </c>
       <c r="D16" t="n">
-        <v>0.84</v>
+        <v>84.5086</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9399999999999999</v>
+        <v>93.61499999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.98</v>
+        <v>98.3686</v>
       </c>
       <c r="G16" t="n">
-        <v>0.88</v>
+        <v>88.1007</v>
       </c>
       <c r="H16" t="n">
-        <v>0.92</v>
+        <v>92.0314</v>
       </c>
       <c r="I16" t="n">
-        <v>0.95</v>
+        <v>94.91</v>
       </c>
       <c r="J16" t="n">
-        <v>0.89</v>
+        <v>89.12860000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.87</v>
+        <v>87.1797</v>
       </c>
     </row>
   </sheetData>
